--- a/src/attributions/attributions_ig_traj_59.xlsx
+++ b/src/attributions/attributions_ig_traj_59.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG15"/>
+  <dimension ref="A1:GG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1505505670556594</v>
+        <v>0.04953918524822731</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004654563194845481</v>
+        <v>-0.01689345831062306</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07130034407667921</v>
+        <v>-0.01190763556069015</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2061892876656778</v>
+        <v>0.1386993470949547</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.02859349158009</v>
+        <v>-0.06059617244167292</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2376686764659408</v>
+        <v>-0.03107964027305992</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0597267323186385</v>
+        <v>0.01504221241060984</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02734127586073692</v>
+        <v>-0.03652965367196639</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01444308604489177</v>
+        <v>-0.007160967763767056</v>
       </c>
       <c r="AB2" t="n">
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.08986635352087068</v>
+        <v>-0.04648821765296862</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1188995835190117</v>
+        <v>-0.07153328462131632</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.01068881697504166</v>
+        <v>0.03133852924264546</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05385711404170328</v>
+        <v>0.03734754379874338</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,25 +1119,25 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.08943304339300873</v>
+        <v>0.001423233583903382</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.05868547334314993</v>
+        <v>0.0001940272043884665</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5278471725053943</v>
+        <v>0.2145172657606749</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
@@ -1146,25 +1146,25 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.289740436006772</v>
+        <v>-0.03956886214228302</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.1615335819894584</v>
+        <v>-0.005923113744402731</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01766238962978282</v>
+        <v>-0.01182512371432242</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,118 +1173,118 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.03664208855633073</v>
+        <v>-0.01955906143743048</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.106320064868756</v>
+        <v>-0.02363685223956992</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0001129973417104904</v>
+        <v>0.007540427896469636</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1717061554689283</v>
+        <v>0.04462311284335635</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.05094839779596284</v>
+        <v>0.01775150996724809</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2998294811119067</v>
+        <v>0.09968207684556034</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0448275512061117</v>
+        <v>-0.03107406347516889</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.03680066603690779</v>
+        <v>-0.02965753429463765</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.08944424399262639</v>
+        <v>-0.05297920217842052</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.00959283539235737</v>
+        <v>0.01997433045954362</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.1282152809884019</v>
+        <v>0.02485061825833825</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.006509052748947679</v>
+        <v>-0.04822459412805353</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.07979969576836606</v>
+        <v>0.01474305538036446</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,67 +1293,67 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.01483817945573064</v>
+        <v>0.021002837338117</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.09635976907283363</v>
+        <v>-0.05410176554311474</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.009136627626927789</v>
+        <v>0.01212982902574267</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.101895572548368</v>
+        <v>0.02743160623572115</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1268568037580275</v>
+        <v>-0.08786551874959699</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08822630295490798</v>
+        <v>0.0005850934174730956</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.05904138530443596</v>
+        <v>-0.0006381770704659295</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.05263886606247567</v>
+        <v>-0.02507370296331712</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.06778255161584938</v>
+        <v>0.04373811322895835</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.09452220992270077</v>
+        <v>0.03409574818615308</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.2470558807294249</v>
+        <v>-0.04706653752243353</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.006790752693319028</v>
+        <v>-0.02088098068369288</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.01371566961202954</v>
+        <v>0.0005794629516005878</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.003959676114675338</v>
+        <v>-0.03800249172348121</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.003127148812192656</v>
+        <v>-0.0054287528199461</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,70 +1425,70 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1610287290621881</v>
+        <v>0.01604619745787586</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.05777571015271534</v>
+        <v>-0.01470293168536311</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.05684625172634084</v>
+        <v>0.02370850890644232</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.07316241405913311</v>
+        <v>0.03683497355175453</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1014212317873641</v>
+        <v>-0.06779063201693829</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.008676429952010213</v>
+        <v>0.0114924414593641</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.09711316120641741</v>
+        <v>0.02317911849359871</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.03855463447968253</v>
+        <v>0.04103175666844702</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,7 +1497,7 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1197466929402745</v>
+        <v>0.01514204744779266</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
@@ -1509,40 +1509,40 @@
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0.01445956613423726</v>
+        <v>0.04905059646434792</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.001165121217931444</v>
+        <v>-0.01281908880417522</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.01326547973392907</v>
+        <v>0.003718717019785231</v>
       </c>
       <c r="FU2" t="n">
         <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.03003970702533485</v>
+        <v>0.003168458712873725</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.07701434412771588</v>
+        <v>-0.03831537504078146</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,19 +1551,19 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.0290528192669455</v>
+        <v>-0.01439526329612235</v>
       </c>
     </row>
     <row r="3">
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2939334330060631</v>
+        <v>0.001853990033313116</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09834510472089884</v>
+        <v>-0.0004263166944411283</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1484578239553835</v>
+        <v>-0.0005060440079542325</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2736,106 +2736,106 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3687488732362041</v>
+        <v>0.00589213666755216</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1365766978466754</v>
+        <v>-0.0005352699787881501</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2273912955957766</v>
+        <v>-0.002805896731932409</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.235000586824576</v>
+        <v>-0.0009882257451320788</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3028184857099551</v>
+        <v>-0.002564757322610755</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.08119586070845694</v>
+        <v>0.0002922426050004606</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2099908695108041</v>
+        <v>-0.003211011557465797</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1750081922349443</v>
+        <v>-0.005526509421791723</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.01708546013515401</v>
+        <v>-0.001023443684810448</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1023086717461457</v>
+        <v>0.0001371732093522791</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08159618809917375</v>
+        <v>-0.0005922909256480063</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.07103383096984239</v>
+        <v>-0.0003788674802840787</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,34 +2844,34 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5485746473784007</v>
+        <v>0.009947520966808253</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2644649897842642</v>
+        <v>0.0008405733495956764</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.4671978961945819</v>
+        <v>-0.0005614739060705612</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01794257900166487</v>
+        <v>-0.00109766024875169</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.08956087055403558</v>
+        <v>-0.001043834455792891</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001248134144527219</v>
+        <v>-4.736122331328076e-05</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.05535952121850041</v>
+        <v>0.001735891283554014</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1591319774615057</v>
+        <v>0.002413390762329206</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.06367188805085153</v>
+        <v>-0.0008684716191549833</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2278572116123212</v>
+        <v>0.004543782841682943</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.2154570257481551</v>
+        <v>0.0003011530665314366</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.2266627531276529</v>
+        <v>-0.0005497771557944317</v>
       </c>
       <c r="CB5" t="n">
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1744227966218452</v>
+        <v>-0.0006165558666928439</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.07100188304852459</v>
+        <v>1.585813958013605e-05</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.09805872380143084</v>
+        <v>0.0004727135027965181</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2976,25 +2976,25 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.04715513113458844</v>
+        <v>-0.002649673339296765</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.2964845684965526</v>
+        <v>-0.001213338791403622</v>
       </c>
       <c r="CR5" t="n">
         <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.05089386119512257</v>
+        <v>-0.0004599253850399714</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
@@ -3003,10 +3003,10 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1646887700307956</v>
+        <v>-0.0007299294127320206</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
@@ -3015,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01706120157771941</v>
+        <v>-0.0005099047025201665</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.126066754743504</v>
+        <v>0.0008778494245746608</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1797384369046598</v>
+        <v>-0.002109885753577562</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,25 +3042,25 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.06023602199122875</v>
+        <v>-0.003050501626103996</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0496609706012402</v>
+        <v>-0.0002527974300904967</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1204975106065354</v>
+        <v>0.0002453524466359568</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,40 +3069,40 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.02313457001156467</v>
+        <v>0.001477810185180223</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.02055422561204918</v>
+        <v>0.00238470827900884</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.2955388746224383</v>
+        <v>-0.0003799199054572945</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.06837405459585301</v>
+        <v>-0.001232134293599711</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.05884099821896189</v>
+        <v>0.002930549447221267</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3111,25 +3111,25 @@
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01228640712928496</v>
+        <v>-0.0008459787334818684</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.02854378993649561</v>
+        <v>-0.0007218542682543206</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.1724187056103949</v>
+        <v>-0.0006007469398949207</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.07846969704348596</v>
+        <v>-0.0005285130019771518</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.05057322920653099</v>
+        <v>-0.0004341266243176695</v>
       </c>
       <c r="ET5" t="n">
         <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.03642689064997195</v>
+        <v>0.002360147735049587</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1731589850756152</v>
+        <v>-0.001541139766480484</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.002886822796630014</v>
+        <v>-0.0008677320163961815</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.1145589768184731</v>
+        <v>0.0007392843434269963</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,85 +3192,85 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001128781563283189</v>
+        <v>0.001484430919655602</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.107749271529264</v>
+        <v>0.0003787821461554866</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.008743905457148799</v>
+        <v>-0.0006049837085988964</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.02173423815206889</v>
+        <v>5.474465980773315e-06</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01616557256508216</v>
+        <v>-1.891436299461767e-05</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.05607069862308683</v>
+        <v>0.00180057427712321</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.08045626614966546</v>
+        <v>-0.0002851949728612323</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.08374275854268882</v>
+        <v>0.00236794737702989</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3725845746060912</v>
+        <v>0.2433647529904485</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.259543112963186</v>
+        <v>-0.2246971458067958</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002717054110001609</v>
+        <v>-0.001899870962946318</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3832290526169136</v>
+        <v>0.3611840340339305</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2766226983071297</v>
+        <v>-0.2670510150932192</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05789616074205783</v>
+        <v>-0.04071640801367201</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.173542292978194</v>
+        <v>0.1208681628547299</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0008579052554468762</v>
+        <v>-0.03194709213339163</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1339691339636241</v>
+        <v>-0.03015707387134341</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,52 +3925,52 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1421567878373126</v>
+        <v>-0.05762577678712217</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002780528837965746</v>
+        <v>-0.188150443846286</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0411176215057536</v>
+        <v>-0.07748166240976105</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02257893388643727</v>
+        <v>0.2014893319332993</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1499664925294286</v>
+        <v>-0.08657691131385518</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07116230149838997</v>
+        <v>0.150250126669384</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5428319059467455</v>
+        <v>0.3849675386691933</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.07906947110064616</v>
+        <v>-0.2232166261500249</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.3093912907455337</v>
+        <v>-0.1403768137961156</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0184381074800834</v>
+        <v>-0.03515922621218155</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.06506879361147395</v>
+        <v>-0.07707458884701904</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0792914100423706</v>
+        <v>-0.04293605292307895</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4036,76 +4036,76 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02162087122650537</v>
+        <v>-0.0301703489753926</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.03482648557407864</v>
+        <v>0.04502997616596781</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1359107406703116</v>
+        <v>-0.00574867552811183</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2628076421199608</v>
+        <v>0.3562452899804754</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01209595313755546</v>
+        <v>-0.1290012766779273</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.177839996723677</v>
+        <v>-0.03025643784601509</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1418893765858864</v>
+        <v>-0.1292871624541134</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.04182994586981221</v>
+        <v>0.1610807227906191</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02390688800382643</v>
+        <v>-0.03545929505043578</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
@@ -4117,19 +4117,19 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>9.839624862665087e-05</v>
+        <v>-0.07687636623550569</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.2415668110569389</v>
+        <v>0.3865453121763849</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1964708016063676</v>
+        <v>0.1925116944500714</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1344909550811472</v>
+        <v>-0.1312694552410718</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.07925041000763214</v>
+        <v>0.1621765354249337</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02252883702210371</v>
+        <v>-0.013590663887542</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.09474514486830884</v>
+        <v>-0.1670872289035032</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.03519354411583256</v>
+        <v>0.06765848033110669</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.02743102993788998</v>
+        <v>-0.0877816744282531</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01525027657453345</v>
+        <v>-0.04414448414502632</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1196316733406086</v>
+        <v>0.03869272144063531</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.09334670204934892</v>
+        <v>-0.0245282335308685</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4222,79 +4222,79 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.07504025519021867</v>
+        <v>-0.001825779967784762</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.03853191626258758</v>
+        <v>-0.1205795328089894</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.04593850622844436</v>
+        <v>-0.122042842997654</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1433139879615967</v>
+        <v>-0.1082249385967345</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05106619073822127</v>
+        <v>0.1457059429411694</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1036815705441234</v>
+        <v>0.02485238603714482</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1379337487356978</v>
+        <v>-0.1005854411664923</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.09580726711019463</v>
+        <v>0.07055365155272857</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.002209771933249634</v>
+        <v>0.02448197502282884</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,22 +4306,22 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1386632500919864</v>
+        <v>-0.1576645801885585</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03851356755621342</v>
+        <v>0.1892436814044498</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.02546238360486076</v>
+        <v>-0.03286932805941544</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4330,82 +4330,82 @@
         <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.0213010717355136</v>
+        <v>-0.1133203952331136</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1316752184006118</v>
+        <v>0.1246685286734388</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.04123610556152175</v>
+        <v>0.05366541117154065</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.008336470404735995</v>
+        <v>-0.02892887872910467</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.06309224229744859</v>
+        <v>0.03372640165240852</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.00323654274225994</v>
+        <v>0.03000942623096704</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.03433130491143796</v>
+        <v>-0.20021456738099</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.139160982153762</v>
+        <v>0.08297301061302688</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,25 +4416,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2098219203243204</v>
+        <v>0.377758206809813</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0554457107785432</v>
+        <v>-0.03222645895153885</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1358499015706202</v>
+        <v>-0.1154762460538458</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,34 +4443,34 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1867242498532026</v>
+        <v>0.615458603263076</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.04463788935329092</v>
+        <v>-0.1320989609356369</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2220572937342664</v>
+        <v>-0.1721498480598662</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02426517572274671</v>
+        <v>0.1982015994678743</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,79 +4479,79 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.04967863050142304</v>
+        <v>-0.1228455260518534</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01077725710532491</v>
+        <v>-0.02823104154242957</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.04989625836079243</v>
+        <v>0.09808325403579947</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01918968617398542</v>
+        <v>-0.4009202282355833</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.003666010958541211</v>
+        <v>-0.1403333692933144</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02728168806477428</v>
+        <v>0.2724156003578097</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.04740920663984543</v>
+        <v>0.09775156681206738</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05643769157114065</v>
+        <v>-0.09389722239874428</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2480616430130204</v>
+        <v>0.9637678378398745</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
@@ -4560,16 +4560,16 @@
         <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.07152306619987478</v>
+        <v>-0.1287118592528402</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.2089821928389345</v>
+        <v>-0.2973935926106199</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04726030471947716</v>
+        <v>-0.08226413892982869</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,64 +4587,64 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.03409479360368884</v>
+        <v>-0.1128680561896767</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.01708114469463832</v>
+        <v>-0.02584121040568887</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04706651452913339</v>
+        <v>0.0295073462544606</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0115735538647852</v>
+        <v>0.07389231068059389</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01200110100258337</v>
+        <v>-0.02178592262393411</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1118254362713853</v>
+        <v>0.6623671947027786</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.02970730650279333</v>
+        <v>-0.09481760591738826</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.06842970122049274</v>
+        <v>-0.1872927508307186</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,61 +4659,61 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.06735158745351498</v>
+        <v>-0.271640893756931</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.005217787141389391</v>
+        <v>0.06619950948341277</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.07285421401743651</v>
+        <v>0.1218384649248102</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01368013401575661</v>
+        <v>-0.5778123874650378</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0004181381727400802</v>
+        <v>0.3780198171580221</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.03167495727088761</v>
+        <v>0.2535263338183129</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.04995997789905782</v>
+        <v>-0.2484863702422433</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,16 +4722,16 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.01017493194571166</v>
+        <v>0.02203676889499027</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.07613711348980291</v>
+        <v>0.1025238471684493</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.003258924467516595</v>
+        <v>-0.06627488749777499</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0918609942037079</v>
+        <v>-0.2793309238529943</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.07203609805197146</v>
+        <v>-0.001108038766381351</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,31 +4761,31 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01776369243068299</v>
+        <v>-0.137400481898321</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0287565305330577</v>
+        <v>0.1051118797866162</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01028642236770301</v>
+        <v>0.03165045847983562</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02753782216325422</v>
+        <v>0.05474695077951921</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,16 +4803,16 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01119764927145801</v>
+        <v>0.03343840275544512</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.06917893443235842</v>
+        <v>-0.1416775069488087</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,19 +4821,19 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.05844582841761393</v>
+        <v>-0.03541527894692273</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.01658149620704855</v>
+        <v>-0.1013427128053905</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0278513050814305</v>
+        <v>0.02900646209740171</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4842,52 +4842,52 @@
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.00178693078020591</v>
+        <v>-0.07225855474868222</v>
       </c>
       <c r="EQ8" t="n">
         <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.01630830452707939</v>
+        <v>-0.1009957181273947</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.06947834568203091</v>
+        <v>-0.004074036485330562</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.04494746635385594</v>
+        <v>-0.2767966980172041</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.005223347479417658</v>
+        <v>0.01248800220505187</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.06919213724088642</v>
+        <v>0.08756308307071363</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
@@ -4896,13 +4896,13 @@
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02933311231684581</v>
+        <v>-0.3188040011507899</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,37 +4911,37 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03209456564861778</v>
+        <v>0.143063062473722</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03468625712510191</v>
+        <v>0.09350562384003239</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.004958060539835554</v>
+        <v>-0.06901662788877987</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.003612888989611431</v>
+        <v>0.0006593454545835934</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.08533008237950142</v>
+        <v>0.124809883862769</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,13 +4950,13 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02275511794868109</v>
+        <v>-0.1616635652123532</v>
       </c>
       <c r="GA8" t="n">
         <v>-0</v>
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.04887518320455314</v>
+        <v>-0.05383671449421399</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -5554,25 +5554,25 @@
         <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.183487051013847</v>
+        <v>0.0138374142574798</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2196011410260475</v>
+        <v>-0.006185772043886288</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1738351955027857</v>
+        <v>-0.005133215020758653</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -5581,61 +5581,61 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1554417992930762</v>
+        <v>0.02157581669632422</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3731321366438238</v>
+        <v>-0.01471902219160342</v>
       </c>
       <c r="O10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2820484165581886</v>
+        <v>-0.01500436991280678</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.208566713226444</v>
+        <v>0.01130694144006839</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.2044167597277437</v>
+        <v>-0.01031187228130568</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.02199296580163132</v>
+        <v>-0.005482852465122985</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.220494647965002</v>
+        <v>-0.00784818400883848</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -5644,16 +5644,16 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0131616605906445</v>
+        <v>-0.01763174106480084</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.08648842334018647</v>
+        <v>0.003791359607541441</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -5662,115 +5662,115 @@
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.03735937101886529</v>
+        <v>0.01219291991982009</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1257045148271228</v>
+        <v>0.002953787624497086</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
         <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.1746342902423368</v>
+        <v>-0.001216774275554841</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.2854857663919859</v>
+        <v>0.03531389735617342</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.1809645964662637</v>
+        <v>-0.001695331348656452</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.05031751201903615</v>
+        <v>-0.007934985098321913</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04453587793781395</v>
+        <v>-0.006785219602798126</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.169126838947675</v>
+        <v>-0.01166372946826592</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.05186157027273851</v>
+        <v>-0.0005943570463497987</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.07598436488574634</v>
+        <v>0.004063001807540157</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.1073518670869561</v>
+        <v>0.008384818945206611</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>-0.06495935040076045</v>
+        <v>0.004202660618773241</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.1872095815197263</v>
+        <v>0.02944561888187393</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
@@ -5779,16 +5779,16 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.03459484906351565</v>
+        <v>-0.002392482759693751</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0.0389054794353229</v>
+        <v>-0.01133955092455834</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,43 +5797,43 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1193315516305861</v>
+        <v>-0.004881857131826267</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.08075899402138585</v>
+        <v>0.004292049413718781</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.1104070163873277</v>
+        <v>0.003649946970492392</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.05434132841487018</v>
+        <v>-0.01143108355625044</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.2625960161782161</v>
+        <v>0.01693407719788757</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.05031281619386367</v>
+        <v>0.003838609192608736</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.09330062010866792</v>
+        <v>-0.004672983219195841</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
@@ -5860,70 +5860,70 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.03661644892977944</v>
+        <v>0.00454023766748669</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.07577978699283296</v>
+        <v>0.006149818738484132</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.4485774196504685</v>
+        <v>-0.003035167014924765</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.08576324488875078</v>
+        <v>0.002385268743958596</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.04854183500605225</v>
+        <v>0.0004035180276142784</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.04397157960353682</v>
+        <v>-0.008471280586768591</v>
       </c>
       <c r="DP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.05120378636647788</v>
+        <v>-0.002430013210189019</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.06865675496244718</v>
+        <v>0.001345674459071535</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
@@ -5932,34 +5932,34 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.3058893735844032</v>
+        <v>0.005819062964484299</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.03212028493672482</v>
+        <v>-0.009110701265322367</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.05761282577452911</v>
+        <v>-0.01094067235456976</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.04499211036320484</v>
+        <v>0.004667489533711384</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
@@ -5968,16 +5968,16 @@
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.01112181024708072</v>
+        <v>-0.002151708738459377</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0.1455134544900163</v>
+        <v>-0.00113215944024245</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
@@ -5986,25 +5986,25 @@
         <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.01076235495041374</v>
+        <v>-0.003011367355170386</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.09170656633769206</v>
+        <v>-0.004224456351326321</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.1885384257497446</v>
+        <v>0.003765259781502095</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
@@ -6013,7 +6013,7 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1069491389651594</v>
+        <v>-0.005163249740197941</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,16 +6022,16 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.04821574723001008</v>
+        <v>0.0009910740115949735</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.1025250946402565</v>
+        <v>0.005746051213378739</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
@@ -6040,25 +6040,25 @@
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.06666527191444906</v>
+        <v>0.002089421967885272</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.03849389153650914</v>
+        <v>0.009525130234182283</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.1847939963620685</v>
+        <v>-0.002699442199959196</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
@@ -6067,25 +6067,25 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.02429182531980972</v>
+        <v>-0.0008344967960833114</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.05808899094938206</v>
+        <v>0.002759116914156647</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.08835513326851638</v>
+        <v>0.004248216401799195</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
@@ -6094,25 +6094,25 @@
         <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.124278320386166</v>
+        <v>-0.009436742649394515</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.1925129000624192</v>
+        <v>-0.003774004295673045</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6120,19 +6120,19 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>-0.3508999968974668</v>
       </c>
       <c r="B11" t="n">
-        <v>0.28270487639867</v>
+        <v>0.3446070705861443</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07821842826235728</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06710311730514061</v>
+        <v>-0.09704029561129018</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6144,28 +6144,28 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.2435648847543714</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3818845055283671</v>
+        <v>0.5300788856708588</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1751918774557598</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.12546020946456</v>
+        <v>-0.1205886446259077</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,19 +6174,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0</v>
+        <v>0.06562494284860773</v>
       </c>
       <c r="T11" t="n">
-        <v>0.126017638857666</v>
+        <v>0.05674305419952445</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.03937778619427939</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1132443205796499</v>
+        <v>0.1384196275917604</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,31 +6195,31 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>-0.2048030714761543</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1428173961477111</v>
+        <v>-0.1138870714818369</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.02931830217075235</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.02991296555078759</v>
+        <v>-0.2742150452428171</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,76 +6228,76 @@
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0.001131904330653974</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.08058499467771686</v>
+        <v>0.306225458431515</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.09817102583271957</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.05251986365568673</v>
+        <v>0.003935419773905835</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0.06505317352056116</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4549887643065977</v>
+        <v>0.3591104676293906</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.06161193511834556</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.224027088175953</v>
+        <v>-0.2099556653702826</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0.327823998265422</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.01234098995157546</v>
+        <v>-0.000386497600683689</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.01158288230218305</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04610221820647297</v>
+        <v>-0.1780463158391044</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
@@ -6309,100 +6309,100 @@
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0.06681858496036928</v>
       </c>
       <c r="BM11" t="n">
-        <v>-0.006221160881281944</v>
+        <v>0.1104408951305418</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.04080426494319626</v>
+        <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.04963032363012862</v>
+        <v>0.1093059415241535</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0.1127170630548383</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2702621022200996</v>
+        <v>0.3740607077855415</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.06220605036294382</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.1402296284318623</v>
+        <v>0.07176059576083682</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>0.1469900156195795</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1279135506926808</v>
+        <v>-0.2150098741182893</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02796422215284798</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.006212953962980843</v>
+        <v>0.01776964642945</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>0</v>
+        <v>-0.02203500485501501</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.03212206713278449</v>
+        <v>-0.3572813379425139</v>
       </c>
       <c r="CO11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.1769111561176158</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.3400773878369656</v>
+        <v>0.2342198484701529</v>
       </c>
       <c r="CR11" t="n">
         <v>0</v>
@@ -6417,46 +6417,46 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0.1167091362295689</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.1261862299527569</v>
+        <v>-0.1990990427148069</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.05440200066467638</v>
+        <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01614247117514328</v>
+        <v>-0.02275325838268029</v>
       </c>
       <c r="DA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.03865094533989448</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.04290008639316878</v>
+        <v>-0.4471487943214227</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.006800918194115516</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0329134692678801</v>
+        <v>-0.01509057076795779</v>
       </c>
       <c r="DJ11" t="n">
         <v>-0</v>
@@ -6471,19 +6471,19 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>0</v>
+        <v>-0.1142275353129538</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04911572072816393</v>
+        <v>-0.07558027949389497</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.07367634915177468</v>
+        <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.08091029850177858</v>
+        <v>0.04651411307862104</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -6498,49 +6498,49 @@
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0</v>
+        <v>0.1970780401439806</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1595540837620641</v>
+        <v>0.3025152618628108</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.003608122638221184</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01522744055943412</v>
+        <v>-0.09822473486748044</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0.01755620958647727</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.09435068197517975</v>
+        <v>-0.01676854649818664</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.08362107541909333</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.09466918716705951</v>
+        <v>-0.07929531650461311</v>
       </c>
       <c r="EK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>0.004257822659473716</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.06784730549782028</v>
+        <v>-0.1573092775835445</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.06481247241346705</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.009151305108737623</v>
+        <v>-0.1087723344762081</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6576,25 +6576,25 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>0.1373554488695645</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1281473947501149</v>
+        <v>-0.2609901655858672</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04570621295985097</v>
+        <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.03383261805416971</v>
+        <v>-0.04615219723580075</v>
       </c>
       <c r="FC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD11" t="n">
         <v>-0</v>
@@ -6603,22 +6603,22 @@
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0.01466150110398772</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03168581981712569</v>
+        <v>0.01676737435508343</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.09259626091539573</v>
+        <v>0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.01109698954528491</v>
+        <v>-0.06929579223330866</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6627,52 +6627,52 @@
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>0.03052754282702927</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.1435077374654557</v>
+        <v>0.03545740129372556</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.2040289953170705</v>
+        <v>0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.2473964751536874</v>
+        <v>0.07449052795557222</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0.1071247610199562</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.004581116203371483</v>
+        <v>-0.2010949008195934</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.06320754178113425</v>
+        <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
         <v>0</v>
@@ -6681,10 +6681,10 @@
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,52 +6692,52 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5307388887622615</v>
+        <v>0.1254307405758765</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2340347155138029</v>
+        <v>-0.08374487267997563</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6033447323471505</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>-0.09469461756836767</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.719286007799245</v>
+        <v>0.1964644461047877</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2275902557869154</v>
+        <v>-0.07011480913253777</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7811891380219527</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-0.1362759214951928</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,76 +6746,76 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0516655124782973</v>
+        <v>0.02802518494319774</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3052451721460922</v>
+        <v>-0.01494497309188206</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1084750298731058</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0.03647008278583066</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1370523319584544</v>
+        <v>-0.05372051769153859</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1035578898747082</v>
+        <v>-0.1690403546206286</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.1325871846654065</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0.02321562697809273</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.3601959898000676</v>
+        <v>0.1707557140143441</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.08783098786021873</v>
+        <v>0.04871619391643624</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.2547691392900532</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>0.02056046889743502</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6827,61 +6827,61 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.9285998674660088</v>
+        <v>0.3359335615888633</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.4005962861134263</v>
+        <v>0.01295695055373195</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.9965959916863888</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>0.009670653057706357</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.09283726051986402</v>
+        <v>-0.1245820146978808</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.05166678853941702</v>
+        <v>-0.09133544597105184</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.06264747157236766</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>-0.03685725007237065</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.05905082703048562</v>
+        <v>-0.01757713027692719</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -6890,16 +6890,16 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.0318221651022554</v>
+        <v>0.05401759518420401</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0.03575733658278441</v>
+        <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0.04097470041136678</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
         <v>-0</v>
@@ -6908,34 +6908,34 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.5760558771321701</v>
+        <v>0.1953029746848315</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.3536698916924904</v>
+        <v>-0.006494263110290126</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.4269447782229301</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0</v>
+        <v>0.001799390936763486</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.240178108835207</v>
+        <v>-0.06453504243427621</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
@@ -6944,25 +6944,25 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.04545121488830707</v>
+        <v>0.02723135920135125</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.2219225416321146</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0.01776744007157463</v>
       </c>
       <c r="CK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.04409864640535684</v>
+        <v>-0.1158530999396503</v>
       </c>
       <c r="CO12" t="n">
         <v>0</v>
@@ -6971,25 +6971,25 @@
         <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.03956319140422408</v>
+        <v>0.02839442336264896</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.04628761964217984</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>-0.1211503760805973</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.2272765586881554</v>
+        <v>-0.06867322940323195</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,70 +6998,70 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.009503901091330091</v>
+        <v>0.03012853091007853</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.2403448066399674</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>0.02875615827022118</v>
       </c>
       <c r="DC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.08320818091165751</v>
+        <v>-0.05839467741269186</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.4071464385148097</v>
+        <v>0.0261489830215154</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.3995559151429467</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0.05478762466971126</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.02729872723595239</v>
+        <v>-0.01088508398385581</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0915156255367431</v>
+        <v>0.04770607441344944</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.04700360718073208</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>0.061186435870825</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
@@ -7070,34 +7070,34 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.2109466679038531</v>
+        <v>0.03709138169558939</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.05376450577445695</v>
+        <v>-0.0399517743666252</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0.1295597863528496</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0</v>
+        <v>0.002461357317767932</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.12274741494656</v>
+        <v>-0.07495656120088802</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
@@ -7106,79 +7106,79 @@
         <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01670781443998904</v>
+        <v>0.02350200891923489</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.07138436971071296</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>-0.02912369390808313</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.08545297534909395</v>
+        <v>-0.03041332038334972</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.07901089585364053</v>
+        <v>0.002084112173589099</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.2573221380555626</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>-0.03788489030112083</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1984287306944342</v>
+        <v>-0.07126743744708222</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.02321802220018319</v>
+        <v>0.003987362179495166</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.1924067484615424</v>
+        <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0.0123386430776305</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.06999248064394656</v>
+        <v>-0.04690248849318164</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,90 +7187,90 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.03502633007520062</v>
+        <v>-0.04680569826470906</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.08869789131018326</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0.02112618947711852</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.3269577001487696</v>
+        <v>-0.02106571572882943</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.2768129032405607</v>
+        <v>-0.006944752556563119</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.1035424914201785</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0.08621525685180312</v>
       </c>
       <c r="FW12" t="n">
         <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.00612282040162653</v>
+        <v>-0.09280171726249747</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.1854821367420795</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>-0</v>
+        <v>0.02903332595813508</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0207271963730053</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.1959895633515499</v>
+        <v>0.7946855457848561</v>
       </c>
       <c r="C13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.05341273425402557</v>
+        <v>-0.4237238866332131</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,22 +7282,22 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.1223681217855377</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.01182269993482197</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3177518128617913</v>
+        <v>1.088874032307315</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.07911048146617555</v>
+        <v>-0.4636245006053605</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -7306,214 +7306,214 @@
         <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0.09103455701783579</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.09005221175588951</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1841703374399801</v>
+        <v>0.1172122082239094</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1530487579066738</v>
+        <v>-0.194868075687148</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0.1628916431507154</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.03343555079378174</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.3536300305024744</v>
+        <v>0.04440713801782483</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.03035497644857942</v>
+        <v>-0.3221816947575351</v>
       </c>
       <c r="AG13" t="n">
         <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.234017315440198e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02989397865255541</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.03057421093300898</v>
+        <v>0.3935291314474967</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.04793615587965603</v>
+        <v>0.1662300112142928</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>-0.07236567183592431</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.08013953698898085</v>
+        <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.3461083443227524</v>
+        <v>1.379265655048477</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.4220769504288404</v>
+        <v>-0.1272462825379391</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>0.01734995860619567</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0307040908073901</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01428757990954472</v>
+        <v>-0.2419456879942206</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03990345935569562</v>
+        <v>-0.3395944821604679</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
         <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0.03266515674517757</v>
       </c>
       <c r="BL13" t="n">
-        <v>-5.892511928936222e-11</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.05222384977488167</v>
+        <v>0.09638461796359922</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.07224924587102194</v>
+        <v>0.1676982010947514</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>0.07926064960448359</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0.09880110782659292</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.2069613082215044</v>
+        <v>0.900792629207944</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.1586387881885104</v>
+        <v>-0.208508338436184</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0.1994524942159107</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.02535174033335516</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.1190595069723024</v>
+        <v>-0.4376947111396399</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.007336953283879726</v>
+        <v>0.1026864023247514</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
@@ -7522,25 +7522,25 @@
         <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>0.06761387467302912</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.05067117539903966</v>
+        <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.005362173163890492</v>
+        <v>-0.7424405238341845</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.2036489857029647</v>
+        <v>0.1211476621293544</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
@@ -7552,22 +7552,22 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>0.0461675011964614</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.003072275549687543</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.1627215908331602</v>
+        <v>-0.405202568979981</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.02546658416904664</v>
+        <v>0.08634653039529384</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
@@ -7576,25 +7576,25 @@
         <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0.09137344958788789</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.005649643024451011</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.1972439085661134</v>
+        <v>-0.2539904655270813</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.01284608845479251</v>
+        <v>0.01717215317672043</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,49 +7606,49 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0.1032040581674171</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.1463003820811239</v>
+        <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01315747972031577</v>
+        <v>-0.2329432981754258</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02134783583441585</v>
+        <v>0.1314682739525904</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0.1505997673738076</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0779897361467308</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.2058186657548506</v>
+        <v>0.3040844856824976</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.1628191738334712</v>
+        <v>-0.1331020960541709</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
@@ -7660,13 +7660,13 @@
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0.1602993514498955</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.287947842716412</v>
+        <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.06652983148514205</v>
+        <v>-0.1554750893280997</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01411119560924581</v>
+        <v>-0.04340756517418611</v>
       </c>
       <c r="EK13" t="n">
         <v>-0</v>
@@ -7684,52 +7684,52 @@
         <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>0.05360143753760279</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.000372388221420907</v>
+        <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.08451263893966227</v>
+        <v>-0.2625521843050678</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.1441270393167078</v>
+        <v>0.04799844002746265</v>
       </c>
       <c r="ET13" t="n">
         <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0.1336918504127063</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.0007004031944649522</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.1638222391009191</v>
+        <v>-0.4889235104907445</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.07743041417255446</v>
+        <v>0.06041285365651648</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
@@ -7738,55 +7738,55 @@
         <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>0.1017946235582725</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0.01538715852654304</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.00678984021514874</v>
+        <v>-0.1655392807975699</v>
       </c>
       <c r="FI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.171295350724737</v>
+        <v>-0.1178055438966</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>-0.1326629753173917</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.08164227274941453</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.2529432286840374</v>
+        <v>-0.00507593994740739</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.1662959496082781</v>
+        <v>0.03655970088712118</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
@@ -7795,13 +7795,13 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>-0.05374088220705051</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.05449761060904049</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.1281600597257112</v>
+        <v>-0.1987301768602446</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
@@ -7816,60 +7816,60 @@
         <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>0</v>
+        <v>0.1138856460939854</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.05718861055679393</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009227907190125626</v>
+        <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6423259543135948</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.09275518368790533</v>
+        <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02260931540969211</v>
+        <v>-0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5600050788376763</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -7884,19 +7884,19 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0009481590111112962</v>
+        <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04331704860116422</v>
+        <v>-0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.09789376949760827</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -7905,13 +7905,13 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.04424731397675211</v>
+        <v>-0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -7920,10 +7920,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.002515433134624765</v>
+        <v>-0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.006236783402495514</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -7935,76 +7935,76 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.04518541255179496</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.03031922935845238</v>
+        <v>-0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.07042395267650969</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.1086964319453365</v>
+        <v>-0</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.06732427323889699</v>
+        <v>-0</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.45932260834512</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.01905356341477356</v>
+        <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.01991305749649359</v>
+        <v>-0</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0484395961159366</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.02691241962358821</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
         <v>0</v>
@@ -8028,37 +8028,37 @@
         <v>0</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.092775965117596e-10</v>
+        <v>-0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.02777192535732465</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.04618035998241032</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.04956747087343371</v>
+        <v>-0</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.2357583168823058</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
@@ -8067,58 +8067,58 @@
         <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
         <v>0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.05485596096490696</v>
+        <v>-0</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.02985471297534891</v>
+        <v>-0</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0.1167443404835334</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.03528800615937152</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP14" t="n">
         <v>0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.09917287040825969</v>
+        <v>-0</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.03866458258356667</v>
+        <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>0</v>
@@ -8127,19 +8127,19 @@
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.03176056851017258</v>
+        <v>0</v>
       </c>
       <c r="CX14" t="n">
         <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01319088901322698</v>
+        <v>0</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0.1203251855097659</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8148,52 +8148,52 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.0163700586534911</v>
+        <v>-0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH14" t="n">
         <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.08021676972930443</v>
+        <v>-0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.07632411154131365</v>
+        <v>0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.03431156569112169</v>
+        <v>-0</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.0100513893588427</v>
+        <v>-0</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.0132128469174025</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
         <v>0</v>
@@ -8202,94 +8202,94 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.002574980465766377</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
         <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01650084968969772</v>
+        <v>0</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.1364022206992311</v>
+        <v>0</v>
       </c>
       <c r="EC14" t="n">
         <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
         <v>0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.02044163690456437</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.03644641852749535</v>
+        <v>-0</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.09666656599953322</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
         <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0306755257760563</v>
+        <v>-0</v>
       </c>
       <c r="EQ14" t="n">
         <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.07640871169778173</v>
+        <v>-0</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0158244506210597</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.02675989819674316</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
@@ -8298,25 +8298,25 @@
         <v>0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.04052120545221807</v>
+        <v>-0</v>
       </c>
       <c r="FC14" t="n">
-        <v>-0.1050708255637592</v>
+        <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.07139480290069379</v>
+        <v>-0</v>
       </c>
       <c r="FI14" t="n">
         <v>0</v>
@@ -8325,52 +8325,52 @@
         <v>0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.01351804769543983</v>
+        <v>-0</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0.06667394372977088</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
         <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.02141173212388779</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.1521441515075984</v>
+        <v>-0</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0.1265408032632475</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
         <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.02693235902877917</v>
+        <v>0</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
@@ -8379,19 +8379,19 @@
         <v>0</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.04636749439772883</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,22 +8399,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.5746722056571831</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.2192060261442369</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0</v>
+        <v>-0.3770322096063226</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.7783179852004463</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.2252306826489875</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0</v>
+        <v>-0.3017677764526085</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8450,73 +8450,73 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.1269292438166021</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.02530412419949435</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0</v>
+        <v>0.1527427923590736</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.0274297435994525</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0.2023384005916475</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0</v>
+        <v>-0.1710430519078312</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>0.4086335337048497</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-0.02633830535589883</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0</v>
+        <v>0.3068411760597838</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
@@ -8525,34 +8525,34 @@
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>0.8524401049978637</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.01920853565258404</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0</v>
+        <v>-0.02497250898007864</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
@@ -8561,22 +8561,22 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>-0.251396012595796</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0.2238300205339419</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0</v>
+        <v>-0.4560436112134714</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
         <v>0</v>
@@ -8585,52 +8585,52 @@
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>-0.001265331282694527</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>-0.11154882278789</v>
       </c>
       <c r="BO15" t="n">
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0</v>
+        <v>0.05474101528205445</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>0.6111970616336514</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>0.02404165922602293</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0</v>
+        <v>0.1017529759412362</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
@@ -8639,73 +8639,73 @@
         <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0</v>
+        <v>-0.3235620740576124</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>0.09240247349530181</v>
       </c>
       <c r="CG15" t="n">
         <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0</v>
+        <v>0.1007779158601315</v>
       </c>
       <c r="CI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0</v>
+        <v>-0.4948242402445944</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>0.1127612875919623</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0</v>
+        <v>0.1871278471786305</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0</v>
+        <v>-0.2852154130378117</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>0.08093470305380751</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0</v>
+        <v>0.05425952270618625</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
@@ -8723,19 +8723,19 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0</v>
+        <v>-0.1712469984537741</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>0.07279171029141264</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0</v>
+        <v>0.04184439332130774</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,22 +8744,22 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0</v>
+        <v>-0.118032508674385</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0.1065782039327341</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0</v>
+        <v>0.1848628007445501</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -8768,28 +8768,28 @@
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0</v>
+        <v>0.3855303077863735</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>0.1142578531081184</v>
       </c>
       <c r="DZ15" t="n">
         <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0</v>
+        <v>-0.2389585525139599</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8798,106 +8798,106 @@
         <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0</v>
+        <v>-0.1333220902116868</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0.0537174658258508</v>
       </c>
       <c r="EI15" t="n">
         <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0</v>
+        <v>0.02724046485755615</v>
       </c>
       <c r="EK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL15" t="n">
         <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0</v>
+        <v>-0.1819190678453665</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0.0133771383171641</v>
       </c>
       <c r="ER15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0</v>
+        <v>-0.01673226807133732</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0</v>
+        <v>-0.3337033038090912</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>0.09124069952503</v>
       </c>
       <c r="FA15" t="n">
         <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0</v>
+        <v>0.06508728210957736</v>
       </c>
       <c r="FC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0</v>
+        <v>0.009528190793854042</v>
       </c>
       <c r="FI15" t="n">
-        <v>0</v>
+        <v>-0.2631695799397709</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0</v>
+        <v>-0.265838078592081</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
@@ -8906,25 +8906,25 @@
         <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0</v>
+        <v>-0.0007761472568129871</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>0.02901766859194947</v>
       </c>
       <c r="FS15" t="n">
         <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0</v>
+        <v>0.0287130963599621</v>
       </c>
       <c r="FU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV15" t="n">
         <v>0</v>
@@ -8939,13 +8939,13 @@
         <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0</v>
+        <v>-0.2239578708527864</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>-0.1520125720901034</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
         <v>0</v>
@@ -8954,12 +8954,2288 @@
         <v>0</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.577655434084647</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.2643638384074483</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.1527057682487686</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.8111276971222101</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.4058784878807286</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.1873326708978648</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.06555336813227684</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.1103909598145177</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.0259402731190805</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.07196356735367172</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.195793537932113</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.0002561692423643004</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.2836577876956328</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.04297936527956783</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.00716822178827979</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.7146455537727826</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.2682679505590169</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.01299783937618188</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.1014373929586498</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.2122749677462362</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-0.1083762209022369</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.04555994162799687</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.07939217114440969</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0.08565629090615742</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.5091469098388766</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0.21239690797688</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>-0.08146349327237438</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0.2456539812695363</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.07404959513903464</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0.05391527938384504</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0.4262152619703426</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.1981653088712298</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>-0.0117792727788269</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0.2201876482667934</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.0332665331524199</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0.05862985071399979</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0.0365816604787897</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0.2009816216943898</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>-0.108119107199457</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0.1282437113020018</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0.03853629387096962</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>-0.01860413440498015</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0.1756500087096073</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0.02443632021362337</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0.1038430518976613</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0.07705680843825792</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0.01649814966522243</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0.0306890177772208</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0.08523943084264829</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0.001224629479843718</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0.1191459329684123</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0.261801772577917</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.02456829800730274</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0.07164922323156502</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>-0.1583879485184508</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0.09780077549633104</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0.1408681807707351</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>-0.006162739090663058</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0.003290905875492382</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0.0002371204371418285</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>-0.128917167613062</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0.111961777873712</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0.5873847612335265</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.7381005493736295</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5395092942435813</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2974380484691188</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.181528648414277</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7135098171533761</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1563718901412445</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.1407958583939717</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.1349384645339801</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.1559626305175825</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.1562669758131554</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.1670480240962215</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1174500799848153</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.2129859954229307</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.07629412757790466</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.05911864294482225</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.5942719550675738</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.548593881236541</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.5340034578211507</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.2257381354409846</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.1149296672408585</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.0131161584211741</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0.126643808795901</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0.2252655343773349</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0.2542796112112491</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0.6994300108301499</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0.1739098157337834</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0.1551584339752676</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.2204924327442005</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0.1714691634071297</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0.1047387035332225</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0.6650031492813279</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0.1531519497968188</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-0.08971063748865052</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0.2448250774609673</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>-0.08592101265199384</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>-0.1588166246591974</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0.7300657454776311</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0.01675616179231394</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>-0.2502927522557705</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0.1944570617183796</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>0.243157000712323</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>-0.2838756301962416</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>-0.2584869386287805</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0.03016127843615058</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0.03408027021590894</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0.0418822847344224</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0.06331014641732621</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0.2436002814582197</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0.03688039388570499</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>0.1647263934574253</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>-0.1359071406635451</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>0.3354875232463282</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>-0.07591085981240273</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>-0.02516915411337342</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.1708911178530726</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0.5879492534774952</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0.04340954177603375</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>-0.0378254119672702</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>-0.0453653309023947</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>-0.1538022538334646</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0.3390774998285723</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.1782575556316086</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.06866410210396487</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.144477666359935</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.161091311803886</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.01325927826014638</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.2958238329667084</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.06781851629285852</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.04095471510350762</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.03290276129468536</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.01069531461154429</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.09181193421206942</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.2027533204365479</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.1685067055171907</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.03804249296158305</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.02189966300884886</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.1835289762356869</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.1077996522875927</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.2214011725233143</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.02444705605575395</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.04999687936820153</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-0.08373067216427613</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.06334202739978846</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.006442005133271267</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.07711367695122945</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0.2029384101363202</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>-0.04438093951567273</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>-0.1083552462110269</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>-0.03982711680415539</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-0.0006703946780312041</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0.05208206871647669</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>-0.1153731514017271</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0.1443880004292488</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>0.1872884058159894</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>-0.01480336941029795</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>0.008749265345345786</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>0.05978918453161886</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF19" t="n">
+        <v>-0.003725231651649774</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>-0.02198835115339733</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>-0.061139368006146</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>-0.07298150620770234</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>0.01945856656938233</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>0.05667889187654172</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>0.001373947086024345</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>0.005674894330139922</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>0.03508429351493703</v>
+      </c>
+      <c r="EB19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG19" t="n">
+        <v>0.0706463755766409</v>
+      </c>
+      <c r="EH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI19" t="n">
+        <v>-0.006418700511778753</v>
+      </c>
+      <c r="EJ19" t="n">
+        <v>0.01534533746699929</v>
+      </c>
+      <c r="EK19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP19" t="n">
+        <v>-0.03074179826581801</v>
+      </c>
+      <c r="EQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER19" t="n">
+        <v>0.01336906516859594</v>
+      </c>
+      <c r="ES19" t="n">
+        <v>0.01015285946331402</v>
+      </c>
+      <c r="ET19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY19" t="n">
+        <v>-0.04337859330982961</v>
+      </c>
+      <c r="EZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA19" t="n">
+        <v>0.0057781147117018</v>
+      </c>
+      <c r="FB19" t="n">
+        <v>0.04722667319448313</v>
+      </c>
+      <c r="FC19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH19" t="n">
+        <v>-0.05993821095801371</v>
+      </c>
+      <c r="FI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ19" t="n">
+        <v>0.02133876999067086</v>
+      </c>
+      <c r="FK19" t="n">
+        <v>0.07995232150006516</v>
+      </c>
+      <c r="FL19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ19" t="n">
+        <v>-0.006142619875362692</v>
+      </c>
+      <c r="FR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS19" t="n">
+        <v>0.0519285498464634</v>
+      </c>
+      <c r="FT19" t="n">
+        <v>-0.1196581615483872</v>
+      </c>
+      <c r="FU19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ19" t="n">
+        <v>0.02281529831808673</v>
+      </c>
+      <c r="GA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB19" t="n">
+        <v>-0.0987975490065743</v>
+      </c>
+      <c r="GC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG19" t="n">
         <v>0</v>
       </c>
     </row>
